--- a/Data/2023 Data/AllReports.xlsx
+++ b/Data/2023 Data/AllReports.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BGC Show\Garden-Show\Data\2023 Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3FBA67-ECAD-411D-ADDC-86F427438A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results by Exhibitor" sheetId="1" r:id="rId1"/>
     <sheet name="Results by Class" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="433">
   <si>
     <t>Exhibitor</t>
   </si>
@@ -32,9 +38,6 @@
     <t xml:space="preserve">	2nd in B15</t>
   </si>
   <si>
-    <t xml:space="preserve">	3rd in N1</t>
-  </si>
-  <si>
     <t>Adeline Balharry</t>
   </si>
   <si>
@@ -56,21 +59,12 @@
     <t xml:space="preserve">	2nd in K8</t>
   </si>
   <si>
-    <t xml:space="preserve">	3rd in L4</t>
-  </si>
-  <si>
     <t>Valerie Dean</t>
   </si>
   <si>
-    <t xml:space="preserve">	3rd in C2</t>
-  </si>
-  <si>
     <t>Barbara Dickinson</t>
   </si>
   <si>
-    <t xml:space="preserve">	1st in A25</t>
-  </si>
-  <si>
     <t>Eric Dodd</t>
   </si>
   <si>
@@ -90,9 +84,6 @@
   </si>
   <si>
     <t xml:space="preserve">	2nd in L12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	1st in L15</t>
   </si>
   <si>
     <t>Lynda Dodd</t>
@@ -176,9 +167,6 @@
     <t xml:space="preserve">	Awarded a Rosette for Most Points in section B</t>
   </si>
   <si>
-    <t xml:space="preserve">	Awarded a Rosette for Most Points in section L</t>
-  </si>
-  <si>
     <t>Barbara Douglas</t>
   </si>
   <si>
@@ -237,10 +225,6 @@
 		Best in section C </t>
   </si>
   <si>
-    <t xml:space="preserve">	Winner of Sutherland Cup:
-		Best floral art </t>
-  </si>
-  <si>
     <t>Jen Douglas</t>
   </si>
   <si>
@@ -281,10 +265,6 @@
   </si>
   <si>
     <t xml:space="preserve">	2nd in G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Winner of Hutchison Bros Trophy:
-		Best flowering pot plant for Orchid section D3</t>
   </si>
   <si>
     <t>Kate Downie</t>
@@ -318,9 +298,6 @@
 		Most points in preserves &amp; sweets for 13 points section K</t>
   </si>
   <si>
-    <t xml:space="preserve">	Awarded a Rosette for Most Points in section K</t>
-  </si>
-  <si>
     <t>Karen Grace</t>
   </si>
   <si>
@@ -342,16 +319,9 @@
     <t xml:space="preserve">	1st in K9</t>
   </si>
   <si>
-    <t xml:space="preserve">	Winner of Marielle Barclay Picture:
-		Best entry in preserves &amp; sweets </t>
-  </si>
-  <si>
     <t>Carole Gutteridge</t>
   </si>
   <si>
-    <t xml:space="preserve">	1st in N1</t>
-  </si>
-  <si>
     <t>Viv Haylock</t>
   </si>
   <si>
@@ -365,10 +335,6 @@
   </si>
   <si>
     <t xml:space="preserve">	1st in B11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Winner of Barclay Trophy:
-		Best rose </t>
   </si>
   <si>
     <t>Gillian Howarth</t>
@@ -402,40 +368,24 @@
 		Best foliage pot plant for Begonia section D1</t>
   </si>
   <si>
-    <t xml:space="preserve">	Winner of Green Gardener Trophy:
-		Most Points in section A for 7 points with 2 firsts 0 seconds and 1 thirds section A</t>
-  </si>
-  <si>
     <t>Fiona McGill</t>
   </si>
   <si>
     <t xml:space="preserve">	1st in S1</t>
   </si>
   <si>
-    <t xml:space="preserve">	1st in S2</t>
-  </si>
-  <si>
     <t>Rory McGill</t>
   </si>
   <si>
     <t xml:space="preserve">	1st in R1</t>
   </si>
   <si>
-    <t xml:space="preserve">	1st in R2</t>
-  </si>
-  <si>
     <t>Boaz Milligan</t>
   </si>
   <si>
-    <t xml:space="preserve">	1st in Q1</t>
-  </si>
-  <si>
     <t>Josiah Milligan</t>
   </si>
   <si>
-    <t xml:space="preserve">	3rd in Q1</t>
-  </si>
-  <si>
     <t>Mandy Mullender</t>
   </si>
   <si>
@@ -443,9 +393,6 @@
   </si>
   <si>
     <t xml:space="preserve">	3rd in K1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	1st in K10</t>
   </si>
   <si>
     <t>Tony Mullender</t>
@@ -482,21 +429,12 @@
     <t xml:space="preserve">	Awarded a Rosette for Best in section M</t>
   </si>
   <si>
-    <t xml:space="preserve">	Awarded a Rosette for Most Points in section M</t>
-  </si>
-  <si>
     <t>D Munro</t>
   </si>
   <si>
-    <t xml:space="preserve">	2nd in D3</t>
-  </si>
-  <si>
     <t>Eathan Munro</t>
   </si>
   <si>
-    <t xml:space="preserve">	1st in S3</t>
-  </si>
-  <si>
     <t>Lynne Munro</t>
   </si>
   <si>
@@ -557,10 +495,6 @@
     <t xml:space="preserve">	3rd in M5</t>
   </si>
   <si>
-    <t xml:space="preserve">	Winner of Evelyn Littlejohn Trophy:
-		Best in section A </t>
-  </si>
-  <si>
     <t>River Munro</t>
   </si>
   <si>
@@ -573,19 +507,12 @@
     <t xml:space="preserve">	1st in Q3</t>
   </si>
   <si>
-    <t xml:space="preserve">	Winner of Iain MacDonald Cup:
-		Most points by a Young Gardener in Sections Q, R &amp; S for 8 points section Q</t>
-  </si>
-  <si>
     <t>David Narro</t>
   </si>
   <si>
     <t xml:space="preserve">	2nd in A2</t>
   </si>
   <si>
-    <t xml:space="preserve">	1st in B4</t>
-  </si>
-  <si>
     <t>Hazel Narro</t>
   </si>
   <si>
@@ -598,18 +525,12 @@
     <t xml:space="preserve">	3rd in B8</t>
   </si>
   <si>
-    <t xml:space="preserve">	2nd in E1</t>
-  </si>
-  <si>
     <t>Kirsty Neilson</t>
   </si>
   <si>
     <t xml:space="preserve">	2nd in A24</t>
   </si>
   <si>
-    <t xml:space="preserve">	1st in D3</t>
-  </si>
-  <si>
     <t>Lillias Noble</t>
   </si>
   <si>
@@ -619,9 +540,6 @@
     <t xml:space="preserve">	3rd in A2</t>
   </si>
   <si>
-    <t xml:space="preserve">	2nd in A23</t>
-  </si>
-  <si>
     <t>Laura Pierce</t>
   </si>
   <si>
@@ -640,10 +558,6 @@
     <t xml:space="preserve">	3rd in L1</t>
   </si>
   <si>
-    <t xml:space="preserve">	Winner of Archie Peebles Trophy:
-		Best fushsia </t>
-  </si>
-  <si>
     <t>Fran Raw</t>
   </si>
   <si>
@@ -651,9 +565,6 @@
   </si>
   <si>
     <t xml:space="preserve">	2nd in N1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	1st in N2</t>
   </si>
   <si>
     <t>Abernethy School</t>
@@ -715,9 +626,6 @@
 		Most Points in section A for 34 points section A</t>
   </si>
   <si>
-    <t xml:space="preserve">	Awarded a Rosette for Most Points in section A</t>
-  </si>
-  <si>
     <t>Jean Slimon</t>
   </si>
   <si>
@@ -745,9 +653,6 @@
     <t xml:space="preserve">	3rd in L7</t>
   </si>
   <si>
-    <t xml:space="preserve">	1st in L8</t>
-  </si>
-  <si>
     <t>Ray Smillie</t>
   </si>
   <si>
@@ -757,9 +662,6 @@
     <t xml:space="preserve">	1st in L6</t>
   </si>
   <si>
-    <t xml:space="preserve">	3rd in L8</t>
-  </si>
-  <si>
     <t>Julie Spittle</t>
   </si>
   <si>
@@ -782,9 +684,6 @@
   </si>
   <si>
     <t xml:space="preserve">	3rd in B4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	2nd in N2</t>
   </si>
   <si>
     <t>Sue Thomas</t>
@@ -1436,8 +1335,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1485,13 +1384,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1529,7 +1436,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1563,6 +1470,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1597,9 +1505,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1772,15 +1681,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B197"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="100.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="100.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1788,7 +1697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1796,1057 +1705,1057 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="B5" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="B6" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="B7" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="B8" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="B11" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="B12" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="B13" t="s">
+      <c r="B16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="B14" t="s">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="B15" t="s">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
         <v>26</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
-      <c r="B17" t="s">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
-      <c r="B18" t="s">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
-      <c r="B19" t="s">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
-      <c r="B20" t="s">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="2:2">
-      <c r="B21" t="s">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="2:2">
-      <c r="B22" t="s">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="2:2">
-      <c r="B23" t="s">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="2:2">
-      <c r="B24" t="s">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:2">
-      <c r="B25" t="s">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="2:2">
-      <c r="B26" t="s">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="2:2">
-      <c r="B27" t="s">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="2:2">
-      <c r="B28" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="2:2">
-      <c r="B29" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:2">
-      <c r="B30" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="2:2">
-      <c r="B31" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="2:2">
-      <c r="B32" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="B33" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="B34" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="B35" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="B36" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="B37" t="s">
+      <c r="B41" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
-      <c r="B38" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="B39" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="B40" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
         <v>53</v>
       </c>
-      <c r="B41" t="s">
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="B42" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
-      <c r="B43" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
-      <c r="B44" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
-      <c r="B45" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
-      <c r="B46" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
-      <c r="B47" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
-      <c r="B48" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
-      <c r="B49" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
-      <c r="B50" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
-      <c r="B51" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
-      <c r="B52" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
-      <c r="B53" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="B54" t="s">
+      <c r="B59" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
-      <c r="B55" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
-      <c r="B56" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
-      <c r="B57" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
-      <c r="B58" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B65" t="s">
         <v>73</v>
       </c>
-      <c r="B59" t="s">
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
-      <c r="B60" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
-      <c r="B61" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
-      <c r="B62" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
-      <c r="B63" t="s">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
-      <c r="B64" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B71" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
-      <c r="B65" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="B66" t="s">
+      <c r="B72" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
-      <c r="B67" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
-      <c r="B68" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
-      <c r="B69" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B75" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
-      <c r="B70" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
-      <c r="B71" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
-      <c r="A72" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
         <v>88</v>
       </c>
-      <c r="B72" t="s">
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
-      <c r="B73" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="B74" t="s">
+      <c r="B81" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
-      <c r="B75" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
-      <c r="B76" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B83" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
-      <c r="B77" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B84" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
-      <c r="B78" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
-      <c r="B79" t="s">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
-      <c r="B80" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" t="s">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>98</v>
+      </c>
+      <c r="B87" t="s">
         <v>99</v>
       </c>
-      <c r="B81" t="s">
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
-      <c r="B82" t="s">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B89" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
-      <c r="B83" t="s">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
-      <c r="B84" t="s">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="B85" t="s">
+      <c r="B91" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
-      <c r="B86" t="s">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B92" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
-      <c r="A87" t="s">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B93" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B94" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B95" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B96" t="s">
         <v>109</v>
       </c>
-      <c r="B87" t="s">
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B97" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
-      <c r="B88" t="s">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B98" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
-      <c r="B89" t="s">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B99" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
-      <c r="B90" t="s">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91" t="s">
+      <c r="B100" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>115</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B101" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
-      <c r="B92" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="B93" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="B94" t="s">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="B95" t="s">
+      <c r="B102" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
-      <c r="B96" t="s">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B103" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
-      <c r="B97" t="s">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="B98" t="s">
+      <c r="B104" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
-      <c r="B99" t="s">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B105" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
-      <c r="A100" t="s">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B106" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B107" t="s">
         <v>126</v>
       </c>
-      <c r="B100" t="s">
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B108" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
-      <c r="A101" t="s">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B109" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B110" t="s">
         <v>129</v>
       </c>
-      <c r="B101" t="s">
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B111" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
-      <c r="A102" t="s">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B112" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B113" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>135</v>
+      </c>
+      <c r="B114" t="s">
         <v>136</v>
       </c>
-      <c r="B102" t="s">
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B115" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
-      <c r="B103" t="s">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B116" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
-      <c r="A104" t="s">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B117" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B118" t="s">
         <v>140</v>
       </c>
-      <c r="B104" t="s">
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B119" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
-      <c r="B105" t="s">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B120" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
-      <c r="B106" t="s">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B121" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
-      <c r="B107" t="s">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B122" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
-      <c r="B108" t="s">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B123" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
-      <c r="B109" t="s">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B124" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
-      <c r="B110" t="s">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B125" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
-      <c r="B111" t="s">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B126" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
-      <c r="B112" t="s">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B127" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
-      <c r="B113" t="s">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B128" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
-      <c r="A114" t="s">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B129" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B130" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B131" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B132" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>155</v>
+      </c>
+      <c r="B133" t="s">
         <v>156</v>
       </c>
-      <c r="B114" t="s">
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B134" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
-      <c r="B115" t="s">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B135" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
-      <c r="B116" t="s">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="B117" t="s">
+      <c r="B136" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
-      <c r="B118" t="s">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="B119" t="s">
+      <c r="B137" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
-      <c r="B120" t="s">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B138" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
-      <c r="B121" t="s">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B139" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
-      <c r="B122" t="s">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="B123" t="s">
+      <c r="B140" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
-      <c r="B124" t="s">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="B125" t="s">
+      <c r="B141" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
-      <c r="B126" t="s">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B142" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
-      <c r="B127" t="s">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="B128" t="s">
+      <c r="B143" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
-      <c r="B129" t="s">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B144" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
-      <c r="B130" t="s">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B145" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
-      <c r="B131" t="s">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B146" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
-      <c r="B132" t="s">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B147" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
-      <c r="A133" t="s">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>176</v>
+      </c>
+      <c r="B148" t="s">
         <v>177</v>
       </c>
-      <c r="B133" t="s">
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B149" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
-      <c r="B134" t="s">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="B135" t="s">
+      <c r="B150" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
-      <c r="A136" t="s">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B151" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B152" t="s">
         <v>182</v>
       </c>
-      <c r="B136" t="s">
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B153" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
-      <c r="A137" t="s">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B154" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B155" t="s">
         <v>185</v>
       </c>
-      <c r="B137" t="s">
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B156" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
-      <c r="B138" t="s">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B157" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
-      <c r="B139" t="s">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B158" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
-      <c r="A140" t="s">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B159" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B160" t="s">
         <v>190</v>
       </c>
-      <c r="B140" t="s">
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B161" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
-      <c r="A141" t="s">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B162" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B163" t="s">
         <v>193</v>
       </c>
-      <c r="B141" t="s">
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B164" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
-      <c r="B142" t="s">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B165" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
-      <c r="A143" t="s">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B166" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B167" t="s">
         <v>197</v>
       </c>
-      <c r="B143" t="s">
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="B144" t="s">
+      <c r="B168" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
-      <c r="B145" t="s">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B169" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
-      <c r="B146" t="s">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B170" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
-      <c r="B147" t="s">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B171" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
-      <c r="A148" t="s">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B172" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B173" t="s">
         <v>204</v>
       </c>
-      <c r="B148" t="s">
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B174" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
-      <c r="B149" t="s">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B175" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
-      <c r="A150" t="s">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>207</v>
+      </c>
+      <c r="B176" t="s">
         <v>208</v>
       </c>
-      <c r="B150" t="s">
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B177" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
-      <c r="B151" t="s">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="B152" t="s">
+      <c r="B178" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
-      <c r="B153" t="s">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B179" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
-      <c r="B154" t="s">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B180" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
-      <c r="B155" t="s">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B181" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
-      <c r="B156" t="s">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B182" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
-      <c r="B157" t="s">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B183" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
-      <c r="B158" t="s">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B184" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
-      <c r="B159" t="s">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="B160" t="s">
+      <c r="B185" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
-      <c r="B161" t="s">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B186" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
-      <c r="B162" t="s">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B187" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
-      <c r="B163" t="s">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B188" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
-      <c r="B164" t="s">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B189" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
-      <c r="B165" t="s">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B190" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
-      <c r="B166" t="s">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B191" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
-      <c r="B167" t="s">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B192" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
-      <c r="A168" t="s">
+    <row r="193" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B193" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B194" t="s">
         <v>228</v>
       </c>
-      <c r="B168" t="s">
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B195" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
-      <c r="B169" t="s">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B196" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
-      <c r="B170" t="s">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B197" t="s">
         <v>231</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="B171" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="B172" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="B173" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="B174" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="B175" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" t="s">
-        <v>238</v>
-      </c>
-      <c r="B176" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="B177" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" t="s">
-        <v>242</v>
-      </c>
-      <c r="B178" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="B179" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="B180" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="B181" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="B182" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="B183" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="B184" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" t="s">
-        <v>251</v>
-      </c>
-      <c r="B185" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="B186" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="B187" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="B188" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="B189" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="B190" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="B191" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="B192" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="193" spans="2:2">
-      <c r="B193" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="194" spans="2:2">
-      <c r="B194" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="195" spans="2:2">
-      <c r="B195" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="196" spans="2:2">
-      <c r="B196" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="197" spans="2:2">
-      <c r="B197" t="s">
-        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -2855,631 +2764,631 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F126"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" customWidth="1"/>
-    <col min="3" max="5" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="50.6640625" customWidth="1"/>
+    <col min="3" max="5" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="1" customFormat="1">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="B3" t="s">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F3">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="B4" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="F4">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="B5" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="C5" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="B6" t="s">
-        <v>279</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>280</v>
+        <v>247</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
       <c r="B8" t="s">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="C8" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D8" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="B9" t="s">
-        <v>285</v>
+        <v>252</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="F9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="B10" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
       <c r="C10" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>288</v>
+        <v>255</v>
       </c>
       <c r="B11" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="C11" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="B12" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>292</v>
+        <v>259</v>
       </c>
       <c r="B13" t="s">
-        <v>293</v>
+        <v>260</v>
       </c>
       <c r="C13" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="B14" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="C14" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="D14" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="E14" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F14">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="B15" t="s">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="E15" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F15">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="B16" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="C16" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="D16" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="E16" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="F16">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>300</v>
+        <v>267</v>
       </c>
       <c r="B17" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="E17" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="F17">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>302</v>
+        <v>269</v>
       </c>
       <c r="B18" t="s">
-        <v>303</v>
+        <v>270</v>
       </c>
       <c r="C18" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D18" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="F18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="B19" t="s">
-        <v>305</v>
+        <v>272</v>
       </c>
       <c r="C19" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="D19" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="E19" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F19">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>306</v>
+        <v>273</v>
       </c>
       <c r="B20" t="s">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c r="C20" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="E20" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="F20">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="B21" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="E21" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="F21">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>310</v>
+        <v>277</v>
       </c>
       <c r="B22" t="s">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="E22" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F22">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" s="1" customFormat="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" s="1" customFormat="1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>314</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="C26" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="C27" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="C29" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="D29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="C30" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="C31" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D31" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E31" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s">
-        <v>327</v>
+        <v>294</v>
       </c>
       <c r="C32" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>332</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="C35" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D35" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="C36" t="s">
         <v>2</v>
@@ -3488,1117 +3397,1117 @@
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="F36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" s="1" customFormat="1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" s="1" customFormat="1">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s">
-        <v>341</v>
+        <v>308</v>
       </c>
       <c r="C42" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D42" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="E42" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F42">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>342</v>
+        <v>309</v>
       </c>
       <c r="B43" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D43" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F43">
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>344</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
       <c r="C44" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D44" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E44" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F44">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" s="1" customFormat="1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" s="1" customFormat="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>348</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s">
-        <v>349</v>
+        <v>316</v>
       </c>
       <c r="C48" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D48" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E48" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F48">
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s">
-        <v>351</v>
+        <v>318</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D49" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E49" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F49">
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
       <c r="B50" t="s">
-        <v>353</v>
+        <v>320</v>
       </c>
       <c r="C50" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="D50" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="F50">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>354</v>
+        <v>321</v>
       </c>
       <c r="B51" t="s">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="C51" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D51" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E51" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F51">
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="B52" t="s">
-        <v>357</v>
+        <v>324</v>
       </c>
       <c r="C52" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D52" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E52" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F52">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="B53" t="s">
-        <v>359</v>
+        <v>326</v>
       </c>
       <c r="C53" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="D53" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E53" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" s="1" customFormat="1">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" s="1" customFormat="1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>364</v>
+        <v>331</v>
       </c>
       <c r="B59" t="s">
-        <v>365</v>
+        <v>332</v>
       </c>
       <c r="C59" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D59" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="F59">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>366</v>
+        <v>333</v>
       </c>
       <c r="B60" t="s">
-        <v>367</v>
+        <v>334</v>
       </c>
       <c r="C60" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D60" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F60">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>368</v>
+        <v>335</v>
       </c>
       <c r="B61" t="s">
-        <v>369</v>
+        <v>336</v>
       </c>
       <c r="C61" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D61" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="F61">
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" s="1" customFormat="1">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" s="1" customFormat="1">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>372</v>
+        <v>339</v>
       </c>
       <c r="B65" t="s">
-        <v>373</v>
+        <v>340</v>
       </c>
       <c r="C65" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="D65" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F65">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" s="1" customFormat="1">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" s="1" customFormat="1">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>376</v>
+        <v>343</v>
       </c>
       <c r="B69" t="s">
-        <v>377</v>
+        <v>344</v>
       </c>
       <c r="C69" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="D69" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E69" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F69">
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="B70" t="s">
-        <v>379</v>
+        <v>346</v>
       </c>
       <c r="C70" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D70" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E70" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F70">
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" s="1" customFormat="1">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" s="1" customFormat="1">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>382</v>
+        <v>349</v>
       </c>
       <c r="B74" t="s">
-        <v>383</v>
+        <v>350</v>
       </c>
       <c r="C74" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D74" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="E74" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F74">
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>384</v>
+        <v>351</v>
       </c>
       <c r="B75" t="s">
-        <v>385</v>
+        <v>352</v>
       </c>
       <c r="C75" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D75" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="E75" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F75">
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>386</v>
+        <v>353</v>
       </c>
       <c r="B76" t="s">
-        <v>387</v>
+        <v>354</v>
       </c>
       <c r="C76" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D76" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="F76">
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>388</v>
+        <v>355</v>
       </c>
       <c r="B77" t="s">
-        <v>389</v>
+        <v>356</v>
       </c>
       <c r="C77" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="D77" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E77" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F77">
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>390</v>
+        <v>357</v>
       </c>
       <c r="B78" t="s">
-        <v>391</v>
+        <v>358</v>
       </c>
       <c r="C78" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D78" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="E78" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F78">
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>392</v>
+        <v>359</v>
       </c>
       <c r="B79" t="s">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="C79" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D79" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="E79" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="F79">
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>394</v>
+        <v>361</v>
       </c>
       <c r="B80" t="s">
-        <v>395</v>
+        <v>362</v>
       </c>
       <c r="C80" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D80" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="E80" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="F80">
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="B81" t="s">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="C81" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D81" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E81" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F81">
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>398</v>
+        <v>365</v>
       </c>
       <c r="B82" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
       <c r="C82" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D82" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E82" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F82">
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>400</v>
+        <v>367</v>
       </c>
       <c r="B83" t="s">
-        <v>401</v>
+        <v>368</v>
       </c>
       <c r="C83" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="D83" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E83" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="F83">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" s="1" customFormat="1">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" s="1" customFormat="1">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>404</v>
+        <v>371</v>
       </c>
       <c r="B87" t="s">
-        <v>405</v>
+        <v>372</v>
       </c>
       <c r="C87" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D87" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E87" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="F87">
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>406</v>
+        <v>373</v>
       </c>
       <c r="B88" t="s">
-        <v>407</v>
+        <v>374</v>
       </c>
       <c r="C88" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D88" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E88" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F88">
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>408</v>
+        <v>375</v>
       </c>
       <c r="B89" t="s">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="C89" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D89" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E89" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F89">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="B90" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="C90" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D90" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="E90" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F90">
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>412</v>
+        <v>379</v>
       </c>
       <c r="B91" t="s">
-        <v>413</v>
+        <v>380</v>
       </c>
       <c r="C91" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="D91" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E91" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F91">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="B92" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="C92" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D92" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E92" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F92">
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="B93" t="s">
-        <v>417</v>
+        <v>384</v>
       </c>
       <c r="C93" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="D93" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E93" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="F93">
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>418</v>
+        <v>385</v>
       </c>
       <c r="B94" t="s">
-        <v>419</v>
+        <v>386</v>
       </c>
       <c r="C94" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D94" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E94" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F94">
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>420</v>
+        <v>387</v>
       </c>
       <c r="B95" t="s">
-        <v>421</v>
+        <v>388</v>
       </c>
       <c r="C95" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="B96" t="s">
-        <v>423</v>
+        <v>390</v>
       </c>
       <c r="C96" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="B97" t="s">
-        <v>425</v>
+        <v>392</v>
       </c>
       <c r="C97" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F97">
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>426</v>
+        <v>393</v>
       </c>
       <c r="B98" t="s">
-        <v>427</v>
+        <v>394</v>
       </c>
       <c r="C98" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>428</v>
+        <v>395</v>
       </c>
       <c r="B99" t="s">
-        <v>429</v>
+        <v>396</v>
       </c>
       <c r="C99" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D99" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E99" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F99">
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" s="1" customFormat="1">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" s="1" customFormat="1">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>432</v>
+        <v>399</v>
       </c>
       <c r="B103" t="s">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="C103" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="B104" t="s">
-        <v>435</v>
+        <v>402</v>
       </c>
       <c r="C104" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D104" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F104">
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>436</v>
+        <v>403</v>
       </c>
       <c r="B105" t="s">
-        <v>437</v>
+        <v>404</v>
       </c>
       <c r="C105" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="B106" t="s">
-        <v>439</v>
+        <v>406</v>
       </c>
       <c r="C106" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D106" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="F106">
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>440</v>
+        <v>407</v>
       </c>
       <c r="B107" t="s">
-        <v>441</v>
+        <v>408</v>
       </c>
       <c r="C107" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="D107" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E107" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="F107">
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" s="1" customFormat="1">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" s="1" customFormat="1">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>444</v>
+        <v>411</v>
       </c>
       <c r="B111" t="s">
-        <v>445</v>
+        <v>412</v>
       </c>
       <c r="C111" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D111" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="E111" t="s">
         <v>2</v>
@@ -4607,214 +4516,214 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>446</v>
+        <v>413</v>
       </c>
       <c r="B112" t="s">
-        <v>447</v>
+        <v>414</v>
       </c>
       <c r="C112" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="D112" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E112" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F112">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:6" s="1" customFormat="1">
+    <row r="113" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" s="1" customFormat="1">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>449</v>
+        <v>416</v>
       </c>
       <c r="B115" t="s">
-        <v>450</v>
+        <v>417</v>
       </c>
       <c r="C115" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="D115" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="E115" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="F115">
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>451</v>
+        <v>418</v>
       </c>
       <c r="B116" t="s">
-        <v>452</v>
+        <v>419</v>
       </c>
       <c r="C116" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="F116">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>453</v>
+        <v>420</v>
       </c>
       <c r="B117" t="s">
-        <v>454</v>
+        <v>421</v>
       </c>
       <c r="C117" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="F117">
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:6" s="1" customFormat="1">
+    <row r="118" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" s="1" customFormat="1">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>456</v>
+        <v>423</v>
       </c>
       <c r="B120" t="s">
-        <v>457</v>
+        <v>424</v>
       </c>
       <c r="C120" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="F120">
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>458</v>
+        <v>425</v>
       </c>
       <c r="B121" t="s">
-        <v>459</v>
+        <v>426</v>
       </c>
       <c r="C121" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="F121">
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:6" s="1" customFormat="1">
+    <row r="122" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" s="1" customFormat="1">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>461</v>
+        <v>428</v>
       </c>
       <c r="B124" t="s">
-        <v>457</v>
+        <v>424</v>
       </c>
       <c r="C124" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="F124">
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>462</v>
+        <v>429</v>
       </c>
       <c r="B125" t="s">
-        <v>463</v>
+        <v>430</v>
       </c>
       <c r="C125" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="F125">
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>464</v>
+        <v>431</v>
       </c>
       <c r="B126" t="s">
-        <v>465</v>
+        <v>432</v>
       </c>
       <c r="C126" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -4822,5 +4731,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>